--- a/实验设计/中间代码生成/中间代码表格/中间代码生成表.xlsx
+++ b/实验设计/中间代码生成/中间代码表格/中间代码生成表.xlsx
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TypeKind、unsigned、const 参与键；不能把不同类型同数值合并。</t>
+          <t>TypeKind、const 参与键；不能把不同类型同数值合并。</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:340</t>
+          <t>include/minic/interface.hpp:335</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:341</t>
+          <t>include/minic/interface.hpp:336</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:342</t>
+          <t>include/minic/interface.hpp:337</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:343</t>
+          <t>include/minic/interface.hpp:338</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:348</t>
+          <t>include/minic/interface.hpp:343</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:349</t>
+          <t>include/minic/interface.hpp:344</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:350</t>
+          <t>include/minic/interface.hpp:345</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:355</t>
+          <t>include/minic/interface.hpp:350</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:356</t>
+          <t>include/minic/interface.hpp:351</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:361</t>
+          <t>include/minic/interface.hpp:356</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:362</t>
+          <t>include/minic/interface.hpp:357</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:363</t>
+          <t>include/minic/interface.hpp:358</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:364</t>
+          <t>include/minic/interface.hpp:359</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:365</t>
+          <t>include/minic/interface.hpp:360</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:370</t>
+          <t>include/minic/interface.hpp:365</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:371</t>
+          <t>include/minic/interface.hpp:366</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:372</t>
+          <t>include/minic/interface.hpp:367</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:373</t>
+          <t>include/minic/interface.hpp:368</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12292,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:374</t>
+          <t>include/minic/interface.hpp:369</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:375</t>
+          <t>include/minic/interface.hpp:370</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:376</t>
+          <t>include/minic/interface.hpp:371</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12358,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:315</t>
+          <t>include/minic/interface.hpp:310</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:316</t>
+          <t>include/minic/interface.hpp:311</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:317</t>
+          <t>include/minic/interface.hpp:312</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:318</t>
+          <t>include/minic/interface.hpp:313</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:319</t>
+          <t>include/minic/interface.hpp:314</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>include/minic/interface.hpp:324</t>
+          <t>include/minic/interface.hpp:319</t>
         </is>
       </c>
     </row>
